--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488112_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488112_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5907</v>
+        <v>1.2827</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6376</v>
+        <v>-0.605</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0469</v>
+        <v>1.8877</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2894</v>
+        <v>2.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9202</v>
+        <v>3.1122</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3691</v>
+        <v>-0.6123</v>
       </c>
       <c r="J2" t="n">
-        <v>2.105</v>
+        <v>1.9142</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7038</v>
+        <v>2.5493</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5988</v>
+        <v>-0.6351</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1843</v>
+        <v>0.5857</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7836</v>
+        <v>0.5629</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9679</v>
+        <v>0.0228</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.3876</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q2" t="n">
         <v>-3.1716</v>
       </c>
       <c r="R2" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>2.896</v>
+        <v>-0.235</v>
       </c>
       <c r="T2" t="n">
-        <v>3.7042</v>
+        <v>0.0488</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8082</v>
+        <v>-0.2838</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.2071</v>
+        <v>0.6036</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>E. IBADIN SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4981</v>
+        <v>1.0345</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.0354</v>
+        <v>0.8469</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5335</v>
+        <v>0.1876</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5</v>
+        <v>0.5362</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1122</v>
+        <v>0.5611</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6123</v>
+        <v>-0.0249</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9142</v>
+        <v>0.9322</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5493</v>
+        <v>0.2894</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6351</v>
+        <v>0.6428</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5857</v>
+        <v>-0.3961</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5629</v>
+        <v>0.2717</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0228</v>
+        <v>-0.6677</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.5858</v>
+        <v>0.3964</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.1716</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5858</v>
+        <v>0.3964</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0196</v>
+        <v>0.1019</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3816</v>
+        <v>-0.0853</v>
       </c>
       <c r="U3" t="n">
-        <v>0.362</v>
+        <v>0.1872</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. IBADIN SANCHEZ</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8203</v>
+        <v>0.4068</v>
       </c>
       <c r="E4" t="n">
-        <v>0.745</v>
+        <v>0.4818</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0752</v>
+        <v>-0.075</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5362</v>
+        <v>2.2894</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5611</v>
+        <v>1.9202</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0249</v>
+        <v>0.3691</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9322</v>
+        <v>2.105</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2894</v>
+        <v>2.7038</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6428</v>
+        <v>-0.5988</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3961</v>
+        <v>0.1843</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2717</v>
+        <v>-0.7836</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6677</v>
+        <v>0.9679</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3964</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.1716</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1123</v>
+        <v>0.7121</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1872</v>
+        <v>1.5484</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07489999999999999</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5054</v>
+        <v>0.3827</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1046</v>
+        <v>-0.0027</v>
       </c>
       <c r="F5" t="n">
-        <v>0.61</v>
+        <v>0.3854</v>
       </c>
       <c r="G5" t="n">
         <v>0.156</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3494</v>
+        <v>0.2267</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4742</v>
+        <v>0.2496</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1979</v>
+        <v>-0.0399</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1046</v>
+        <v>-0.0027</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.0372</v>
       </c>
       <c r="G6" t="n">
         <v>0.156</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.0707</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2666</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. ESTEVES VEHVILAINEN</t>
+          <t>L. VIVAR MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6975</v>
+        <v>-0.9091</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.6661</v>
+        <v>-0.7462</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9686</v>
+        <v>-0.1629</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1681</v>
+        <v>-1.0512</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0803</v>
+        <v>4.2328</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-5.284</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3485</v>
+        <v>-0.2883</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5644</v>
+        <v>4.3451</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7841</v>
+        <v>-4.6334</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1804</v>
+        <v>-0.7629</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5158</v>
+        <v>-0.1123</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6962</v>
+        <v>-0.6506</v>
       </c>
       <c r="P7" t="n">
         <v>0.3964</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1805</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5769</v>
+        <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2812</v>
+        <v>-0.4506</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8629</v>
+        <v>0.337</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5816</v>
+        <v>-0.7875</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2071</v>
+        <v>0.1962</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1962</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. VIVAR MARTINEZ</t>
+          <t>T. ESTEVES VEHVILAINEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8241</v>
+        <v>-1.7494</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3804</v>
+        <v>-2.8864</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4437</v>
+        <v>1.137</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0512</v>
+        <v>-1.1681</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2328</v>
+        <v>-1.0803</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.284</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2883</v>
+        <v>-1.3485</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3451</v>
+        <v>-0.5644</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.6334</v>
+        <v>-0.7841</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7629</v>
+        <v>0.1804</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1123</v>
+        <v>-0.5158</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6506</v>
+        <v>0.6962</v>
       </c>
       <c r="P8" t="n">
         <v>0.3964</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>-2.1805</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3876</v>
+        <v>2.5769</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3655</v>
+        <v>0.2294</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2972</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0683</v>
+        <v>-0.4132</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1962</v>
+        <v>-1.2071</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1962</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9002</v>
+        <v>-1.8107</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7176</v>
+        <v>-1.7966</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1826</v>
+        <v>-0.0141</v>
       </c>
       <c r="G9" t="n">
         <v>-2.2005</v>
@@ -1156,13 +1156,13 @@
         <v>1.1893</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0316</v>
+        <v>0.1212</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.5526</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5999</v>
+        <v>-0.4314</v>
       </c>
       <c r="V9" t="n">
         <v>0.0704</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9916</v>
+        <v>-2.0601</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2866</v>
+        <v>-3.4674</v>
       </c>
       <c r="F10" t="n">
-        <v>1.295</v>
+        <v>1.4073</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6208</v>
@@ -1234,13 +1234,13 @@
         <v>1.5858</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2328</v>
+        <v>0.1643</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4847</v>
+        <v>0.3039</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2519</v>
+        <v>-0.1396</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1896</v>
+        <v>-3.1376</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4879</v>
+        <v>-1.5482</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7017</v>
+        <v>-1.5894</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4569</v>
@@ -1312,13 +1312,13 @@
         <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2393</v>
+        <v>-0.1872</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6019</v>
+        <v>0.3378</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6373</v>
+        <v>-0.525</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8811</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2124</v>
+        <v>-3.2508</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7721</v>
+        <v>-1.8948</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4402</v>
+        <v>-1.356</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3427</v>
@@ -1390,13 +1390,13 @@
         <v>0.5947</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2066</v>
+        <v>-0.245</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5505</v>
+        <v>0.3268</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6561</v>
+        <v>-0.5718</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2666</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.3329</v>
+        <v>-3.8329</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.4193</v>
+        <v>-5.7228</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0864</v>
+        <v>1.8899</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8614000000000001</v>
@@ -1468,13 +1468,13 @@
         <v>2.3787</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6964</v>
+        <v>-0.1964</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4954</v>
+        <v>0.2012</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.201</v>
+        <v>-0.3976</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.9317</v>
+        <v>-13.6838</v>
       </c>
       <c r="E14" t="n">
-        <v>-18.592</v>
+        <v>-17.3441</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6603</v>
+        <v>3.660299999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-7.063999999999999</v>
@@ -1519,10 +1519,10 @@
         <v>-10.13</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.064300000000001</v>
+        <v>-4.064299999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>4.9072</v>
+        <v>4.907200000000001</v>
       </c>
       <c r="L14" t="n">
         <v>-8.971299999999999</v>
@@ -1546,13 +1546,13 @@
         <v>14.8668</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9361</v>
+        <v>0.3120999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.92</v>
+        <v>4.168</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.8558</v>
+        <v>-3.855700000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-3.9583</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.578900000000001</v>
+        <v>9.303699999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1151</v>
+        <v>6.6244</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4638</v>
+        <v>2.6793</v>
       </c>
       <c r="G15" t="n">
         <v>5.947</v>
@@ -1624,13 +1624,13 @@
         <v>2.5769</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6873</v>
+        <v>0.0376</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2568</v>
+        <v>0.2525</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4304</v>
+        <v>-0.2149</v>
       </c>
       <c r="V15" t="n">
         <v>0.9405</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.9972</v>
+        <v>6.2609</v>
       </c>
       <c r="E16" t="n">
-        <v>5.0911</v>
+        <v>3.3593</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9061</v>
+        <v>2.9015</v>
       </c>
       <c r="G16" t="n">
         <v>5.0308</v>
@@ -1702,13 +1702,13 @@
         <v>3.1716</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5788</v>
+        <v>0.8424</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9003</v>
+        <v>1.1685</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3215</v>
+        <v>-0.326</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6036</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.9282</v>
+        <v>5.8199</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1402</v>
+        <v>2.6496</v>
       </c>
       <c r="F17" t="n">
-        <v>3.788</v>
+        <v>3.1703</v>
       </c>
       <c r="G17" t="n">
         <v>4.1251</v>
@@ -1780,13 +1780,13 @@
         <v>2.5769</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0123</v>
+        <v>0.9039</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0589</v>
+        <v>0.5683</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9533</v>
+        <v>0.3356</v>
       </c>
       <c r="V17" t="n">
         <v>0.1962</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.0579</v>
+        <v>5.422</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8086</v>
+        <v>2.9292</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2492</v>
+        <v>2.4928</v>
       </c>
       <c r="G18" t="n">
         <v>2.5957</v>
@@ -1858,13 +1858,13 @@
         <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2008</v>
+        <v>0.1633</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7488</v>
+        <v>0.3718</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4521</v>
+        <v>-0.2085</v>
       </c>
       <c r="V18" t="n">
         <v>1.4737</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>S. CASTRO BRAVO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4841</v>
+        <v>0.1826</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7613</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2771</v>
+        <v>0.1826</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5782</v>
+        <v>0.1358</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.598</v>
+        <v>0.1358</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0197</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7315</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3381</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6066</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1533</v>
+        <v>0.1358</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2599</v>
+        <v>0.1358</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4132</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3964</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.2606</v>
+        <v>0.0468</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2173</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0432</v>
+        <v>0.0468</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. CASTRO BRAVO</t>
+          <t>N. ALVAREZ ALVAREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1545</v>
+        <v>0.1202</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-0.0624</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1545</v>
+        <v>0.1826</v>
       </c>
       <c r="G21" t="n">
         <v>0.1358</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0187</v>
+        <v>-0.0156</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.0624</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. ALVAREZ ALVAREZ</t>
+          <t>P. CARRASCO LOBO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0921</v>
+        <v>-0.1921</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0624</v>
+        <v>-1.6417</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1545</v>
+        <v>1.4495</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1358</v>
+        <v>-1.7186</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1358</v>
+        <v>-2.0419</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.3232</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-1.8156</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>-1.1767</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0.639</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1358</v>
+        <v>0.097</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1358</v>
+        <v>-0.8652</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0437</v>
+        <v>-0.2753</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0624</v>
+        <v>-0.0421</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0187</v>
+        <v>-0.2332</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. CARRASCO LOBO</t>
+          <t>P. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5643</v>
+        <v>-0.5353</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8454</v>
+        <v>-4.4097</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2811</v>
+        <v>3.8744</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7186</v>
+        <v>-0.2891</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0419</v>
+        <v>-0.7062</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3232</v>
+        <v>0.4171</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8156</v>
+        <v>-1.3273</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1767</v>
+        <v>-0.652</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.639</v>
+        <v>-0.6752</v>
       </c>
       <c r="M23" t="n">
-        <v>0.097</v>
+        <v>1.0381</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8652</v>
+        <v>-0.0542</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9622000000000001</v>
+        <v>1.0923</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5947</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9911</v>
+        <v>-3.1716</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5858</v>
+        <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6475</v>
+        <v>-0.2065</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2458</v>
+        <v>0.0891</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4017</v>
+        <v>-0.2956</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2071</v>
+        <v>1.3479</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.3479</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. RAMOS ANGULO</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4214</v>
+        <v>-0.9643</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6743</v>
+        <v>-0.7668</v>
       </c>
       <c r="F24" t="n">
-        <v>0.253</v>
+        <v>-0.1975</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9563</v>
+        <v>-0.5782</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2274</v>
+        <v>-1.598</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7289</v>
+        <v>1.0197</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5584</v>
+        <v>-0.7315</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0404</v>
+        <v>-1.3381</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5988</v>
+        <v>0.6066</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3979</v>
+        <v>0.1533</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2677</v>
+        <v>-0.2599</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1301</v>
+        <v>0.4132</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3964</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.06859999999999999</v>
+        <v>0.8122</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1248</v>
+        <v>0.6893</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0562</v>
+        <v>0.1229</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ SANCHEZ</t>
+          <t>J. RAMOS ANGULO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.8008</v>
+        <v>-1.3371</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.1228</v>
+        <v>-1.6743</v>
       </c>
       <c r="F25" t="n">
-        <v>3.322</v>
+        <v>0.3372</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2891</v>
+        <v>-0.9563</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7062</v>
+        <v>-0.2274</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4171</v>
+        <v>-0.7289</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.3273</v>
+        <v>-0.5584</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.652</v>
+        <v>0.0404</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6752</v>
+        <v>-0.5988</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0381</v>
+        <v>-0.3979</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0542</v>
+        <v>-0.2677</v>
       </c>
       <c r="O25" t="n">
-        <v>1.0923</v>
+        <v>-0.1301</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.3876</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.1716</v>
+        <v>-0.9911</v>
       </c>
       <c r="R25" t="n">
-        <v>1.784</v>
+        <v>0.5947</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.472</v>
+        <v>0.0156</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.624</v>
+        <v>-0.1248</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8481</v>
+        <v>0.1404</v>
       </c>
       <c r="V25" t="n">
-        <v>1.3479</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.3479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.2398</v>
+        <v>-2.9566</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.3058</v>
+        <v>-5.4909</v>
       </c>
       <c r="F26" t="n">
-        <v>2.066</v>
+        <v>2.5342</v>
       </c>
       <c r="G26" t="n">
         <v>-1.7719</v>
@@ -2482,13 +2482,13 @@
         <v>2.7751</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.0715</v>
+        <v>-0.7883</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.433</v>
+        <v>0.382</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.6385</v>
+        <v>-1.1703</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.9377</v>
+        <v>-5.4366</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.1686</v>
+        <v>-5.7798</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2308</v>
+        <v>0.3431</v>
       </c>
       <c r="G27" t="n">
         <v>-6.1947</v>
@@ -2560,13 +2560,13 @@
         <v>0.9911</v>
       </c>
       <c r="S27" t="n">
-        <v>1.257</v>
+        <v>0.7581</v>
       </c>
       <c r="T27" t="n">
-        <v>1.1749</v>
+        <v>0.5636</v>
       </c>
       <c r="U27" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.1944</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2593,19 +2593,19 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>14.93160000000001</v>
+        <v>16.29</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.660300000000001</v>
+        <v>-3.660400000000002</v>
       </c>
       <c r="F28" t="n">
-        <v>18.5919</v>
+        <v>19.95</v>
       </c>
       <c r="G28" t="n">
-        <v>7.064099999999999</v>
+        <v>7.064099999999995</v>
       </c>
       <c r="H28" t="n">
-        <v>-3.0661</v>
+        <v>-3.066100000000001</v>
       </c>
       <c r="I28" t="n">
         <v>10.13</v>
@@ -2617,7 +2617,7 @@
         <v>1.8412</v>
       </c>
       <c r="L28" t="n">
-        <v>1.1588</v>
+        <v>1.158800000000001</v>
       </c>
       <c r="M28" t="n">
         <v>4.0641</v>
@@ -2629,7 +2629,7 @@
         <v>8.971300000000001</v>
       </c>
       <c r="P28" t="n">
-        <v>2.973399999999999</v>
+        <v>2.9734</v>
       </c>
       <c r="Q28" t="n">
         <v>-14.8667</v>
@@ -2638,13 +2638,13 @@
         <v>17.8401</v>
       </c>
       <c r="S28" t="n">
-        <v>0.9360000000000002</v>
+        <v>2.2942</v>
       </c>
       <c r="T28" t="n">
-        <v>3.855799999999999</v>
+        <v>3.8558</v>
       </c>
       <c r="U28" t="n">
-        <v>-2.9201</v>
+        <v>-1.5616</v>
       </c>
       <c r="V28" t="n">
         <v>3.9582</v>
@@ -2653,7 +2653,7 @@
         <v>4.3507</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.3923999999999999</v>
+        <v>-0.3924</v>
       </c>
     </row>
   </sheetData>
